--- a/3_CGE/Game_theory_2024/0_External_data/Original_forest_treated.xlsx
+++ b/3_CGE/Game_theory_2024/0_External_data/Original_forest_treated.xlsx
@@ -367,7 +367,7 @@
         </is>
       </c>
       <c r="C2" s="0">
-        <v>12166586</v>
+        <v>9458237</v>
       </c>
     </row>
     <row r="3">
@@ -382,7 +382,7 @@
         </is>
       </c>
       <c r="C3" s="0">
-        <v>103843</v>
+        <v>113736</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         </is>
       </c>
       <c r="C4" s="0">
-        <v>14010986</v>
+        <v>14604662</v>
       </c>
     </row>
     <row r="5">
@@ -418,52 +418,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>malasya</t>
+          <t>SAfr</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C6" s="0">
-        <v>0</v>
+        <v>1329160</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>peru</t>
+          <t>malasya</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C7" s="0">
-        <v>2641134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>russia</t>
+          <t>peru</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C8" s="0">
-        <v>218878944</v>
+        <v>1984966</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>brasil</t>
+          <t>russia</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -472,28 +472,28 @@
         </is>
       </c>
       <c r="C9" s="0">
-        <v>0</v>
+        <v>199771118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>eastasia</t>
+          <t>brasil</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C10" s="0">
-        <v>7912607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>indonesia</t>
+          <t>CAfr</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -502,28 +502,28 @@
         </is>
       </c>
       <c r="C11" s="0">
-        <v>33509014</v>
+        <v>32395517</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mexico</t>
+          <t>eastasia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C12" s="0">
-        <v>0</v>
+        <v>7957611</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>russia</t>
+          <t>indonesia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -532,18 +532,18 @@
         </is>
       </c>
       <c r="C13" s="0">
-        <v>0</v>
+        <v>33891235</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>canada</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C14" s="0">
@@ -553,12 +553,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ghana</t>
+          <t>russia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C15" s="0">
@@ -568,12 +568,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>korea</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C16" s="0">
@@ -583,22 +583,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>newzealand</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C17" s="0">
-        <v>2543050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>india</t>
+          <t>ghana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C18" s="0">
-        <v>3903830</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>korea</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C19" s="0">
-        <v>50860905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bolivia</t>
+          <t>newzealand</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="C20" s="0">
-        <v>984833</v>
+        <v>2489337</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>colombia</t>
+          <t>india</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -652,28 +652,28 @@
         </is>
       </c>
       <c r="C21" s="0">
-        <v>967751</v>
+        <v>3286471</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>paraguay</t>
+          <t>us</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C22" s="0">
-        <v>243468</v>
+        <v>47631879</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>indonesia</t>
+          <t>bolivia</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -682,58 +682,58 @@
         </is>
       </c>
       <c r="C23" s="0">
-        <v>0</v>
+        <v>1114115</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>colombia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C24" s="0">
-        <v>4596642</v>
+        <v>986882</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mozambique</t>
+          <t>drc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C25" s="0">
-        <v>3381155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>newzealand</t>
+          <t>paraguay</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C26" s="0">
-        <v>15785</v>
+        <v>849464</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>japan</t>
+          <t>indonesia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -742,58 +742,58 @@
         </is>
       </c>
       <c r="C27" s="0">
-        <v>15359516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mexico</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C28" s="0">
-        <v>12401187</v>
+        <v>4326603</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>uruguay</t>
+          <t>mozambique</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C29" s="0">
-        <v>0</v>
+        <v>4426394</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>myanmar</t>
+          <t>newzealand</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C30" s="0">
-        <v>8124382</v>
+        <v>120540</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>southasia</t>
+          <t>japan</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -802,103 +802,103 @@
         </is>
       </c>
       <c r="C31" s="0">
-        <v>3040171</v>
+        <v>15187971</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>eu27</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C32" s="0">
-        <v>43475112</v>
+        <v>11573934</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>CAfr</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C33" s="0">
-        <v>960199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>myanmar</t>
+          <t>uruguay</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C34" s="0">
-        <v>27442834</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>canada</t>
+          <t>myanmar</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C35" s="0">
-        <v>46574251</v>
+        <v>6746034</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mozambique</t>
+          <t>southasia</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C36" s="0">
-        <v>0</v>
+        <v>1777187</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>uruguay</t>
+          <t>eu27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C37" s="0">
-        <v>0</v>
+        <v>35063139</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ivorycoast</t>
+          <t>EAfr</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -907,58 +907,58 @@
         </is>
       </c>
       <c r="C38" s="0">
-        <v>0</v>
+        <v>1176739</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mozambique</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C39" s="0">
-        <v>0</v>
+        <v>501367</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>restofworld</t>
+          <t>WAfr</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C40" s="0">
-        <v>593888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>southasia</t>
+          <t>myanmar</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C41" s="0">
-        <v>0</v>
+        <v>28637743</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -967,28 +967,28 @@
         </is>
       </c>
       <c r="C42" s="0">
-        <v>0</v>
+        <v>39484390</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mexico</t>
+          <t>NAfr</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C43" s="0">
-        <v>19704816</v>
+        <v>789254</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>peru</t>
+          <t>SAfr</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="C44" s="0">
-        <v>16540398</v>
+        <v>7379223</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ssa</t>
+          <t>mozambique</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1018,22 +1018,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ivorycoast</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C46" s="0">
-        <v>6743391</v>
+        <v>582673</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>brasil</t>
+          <t>uruguay</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1042,18 +1042,18 @@
         </is>
       </c>
       <c r="C47" s="0">
-        <v>146405090</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ghana</t>
+          <t>ivorycoast</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C48" s="0">
@@ -1063,22 +1063,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>china</t>
+          <t>EAfr</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C49" s="0">
-        <v>2837867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>drc</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="C50" s="0">
-        <v>2016529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>angdrc</t>
+          <t>mozambique</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1102,43 +1102,43 @@
         </is>
       </c>
       <c r="C51" s="0">
-        <v>2629533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>argentina</t>
+          <t>restofworld</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C52" s="0">
-        <v>10192554</v>
+        <v>412954</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>colombia</t>
+          <t>southasia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C53" s="0">
-        <v>12443041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>colombia</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1153,37 +1153,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>india</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C55" s="0">
-        <v>0</v>
+        <v>21356305</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>venezuela</t>
+          <t>peru</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C56" s="0">
-        <v>0</v>
+        <v>16514019</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>venezuela</t>
+          <t>ivorycoast</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1192,58 +1192,58 @@
         </is>
       </c>
       <c r="C57" s="0">
-        <v>4923864</v>
+        <v>5538017</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>mena</t>
+          <t>brasil</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C58" s="0">
-        <v>15183</v>
+        <v>148207228</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>southasia</t>
+          <t>ghana</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C59" s="0">
-        <v>4355514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>oceania</t>
+          <t>china</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C60" s="0">
-        <v>0</v>
+        <v>3026715</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>malasya</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="C61" s="0">
-        <v>0</v>
+        <v>2207257</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>oceania</t>
+          <t>colombia</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1267,48 +1267,48 @@
         </is>
       </c>
       <c r="C62" s="0">
-        <v>89588</v>
+        <v>12501970</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>india</t>
+          <t>colombia</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C63" s="0">
-        <v>13077483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ssa</t>
+          <t>india</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C64" s="0">
-        <v>3512880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>madagascar</t>
+          <t>venezuela</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C65" s="0">
@@ -1318,52 +1318,52 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>indonesia</t>
+          <t>venezuela</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C66" s="0">
-        <v>0</v>
+        <v>5054164</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bolivia</t>
+          <t>mena</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C67" s="0">
-        <v>13394567</v>
+        <v>10107</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>venezuela</t>
+          <t>southasia</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C68" s="0">
-        <v>0</v>
+        <v>4704708</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>angdrc</t>
+          <t>oceania</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1378,12 +1378,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>seasia</t>
+          <t>malasya</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C70" s="0">
@@ -1393,12 +1393,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>SAfr</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C71" s="0">
@@ -1408,27 +1408,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>madagascar</t>
+          <t>oceania</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C72" s="0">
-        <v>0</v>
+        <v>87299</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mena</t>
+          <t>WAfr</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C73" s="0">
@@ -1438,27 +1438,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>myanmar</t>
+          <t>india</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C74" s="0">
-        <v>0</v>
+        <v>13067375</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>madagascar</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C75" s="0">
@@ -1468,12 +1468,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>uruguay</t>
+          <t>indonesia</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C76" s="0">
@@ -1483,7 +1483,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>madagascar</t>
+          <t>bolivia</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="C77" s="0">
-        <v>6661204</v>
+        <v>13137260</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>venezuela</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C78" s="0">
-        <v>164615915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>china</t>
+          <t>NAfr</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C79" s="0">
-        <v>98406323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>latinamer</t>
+          <t>seasia</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C80" s="0">
-        <v>33636865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>paraguay</t>
+          <t>EAfr</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C81" s="0">
-        <v>115512</v>
+        <v>8377985</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>malasya</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1567,28 +1567,28 @@
         </is>
       </c>
       <c r="C82" s="0">
-        <v>7921593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>russia</t>
+          <t>CAfr</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C83" s="0">
-        <v>30216161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>restofworld</t>
+          <t>madagascar</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1597,88 +1597,88 @@
         </is>
       </c>
       <c r="C84" s="0">
-        <v>29559666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>eastasia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C85" s="0">
-        <v>1314718</v>
+        <v>10612181</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>argentina</t>
+          <t>mena</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C86" s="0">
-        <v>412352</v>
+        <v>652647</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>brasil</t>
+          <t>myanmar</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C87" s="0">
-        <v>7305830</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>eu27</t>
+          <t>us</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C88" s="0">
-        <v>91115835</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>eastasia</t>
+          <t>uruguay</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C89" s="0">
-        <v>237972</v>
+        <v>1751354</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>efta</t>
+          <t>madagascar</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="C90" s="0">
-        <v>0</v>
+        <v>6887549</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>seasia</t>
+          <t>NAfr</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1702,28 +1702,28 @@
         </is>
       </c>
       <c r="C91" s="0">
-        <v>46729666</v>
+        <v>11172</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>japan</t>
+          <t>us</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C92" s="0">
-        <v>0</v>
+        <v>170018262</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>efta</t>
+          <t>china</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1732,43 +1732,43 @@
         </is>
       </c>
       <c r="C93" s="0">
-        <v>1860332</v>
+        <v>93626647</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>korea</t>
+          <t>latinamer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C94" s="0">
-        <v>7067245</v>
+        <v>33578798</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>bolivia</t>
+          <t>paraguay</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C95" s="0">
-        <v>0</v>
+        <v>230320</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>newzealand</t>
+          <t>malasya</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1777,28 +1777,28 @@
         </is>
       </c>
       <c r="C96" s="0">
-        <v>0</v>
+        <v>7689875</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ssa</t>
+          <t>russia</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C97" s="0">
-        <v>56604905</v>
+        <v>47318704</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>oceania</t>
+          <t>restofworld</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1807,43 +1807,43 @@
         </is>
       </c>
       <c r="C98" s="0">
-        <v>1245358</v>
+        <v>33918291</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ghana</t>
+          <t>eastasia</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C99" s="0">
-        <v>3844410</v>
+        <v>1181906</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>eu27</t>
+          <t>brasil</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C100" s="0">
-        <v>0</v>
+        <v>5080638</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>restofworld</t>
+          <t>angola</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1852,43 +1852,43 @@
         </is>
       </c>
       <c r="C101" s="0">
-        <v>0</v>
+        <v>24049509</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>korea</t>
+          <t>eu27</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tropical</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C102" s="0">
-        <v>0</v>
+        <v>102143219</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>latinamer</t>
+          <t>eastasia</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C103" s="0">
-        <v>3545812</v>
+        <v>188801</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>angdrc</t>
+          <t>efta</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1897,33 +1897,33 @@
         </is>
       </c>
       <c r="C104" s="0">
-        <v>71510223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>canada</t>
+          <t>seasia</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C105" s="0">
-        <v>53261662</v>
+        <v>45419927</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>peru</t>
+          <t>japan</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Tropical</t>
         </is>
       </c>
       <c r="C106" s="0">
@@ -1938,17 +1938,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Boreal</t>
+          <t>Temperate</t>
         </is>
       </c>
       <c r="C107" s="0">
-        <v>20878425</v>
+        <v>3374431</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>korea</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -1957,43 +1957,43 @@
         </is>
       </c>
       <c r="C108" s="0">
-        <v>0</v>
+        <v>7055447</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>seasia</t>
+          <t>angola</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C109" s="0">
-        <v>2066992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>latinamer</t>
+          <t>bolivia</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Temperate</t>
+          <t>Boreal</t>
         </is>
       </c>
       <c r="C110" s="0">
-        <v>6491744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>argentina</t>
+          <t>newzealand</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2008,15 +2008,240 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>oceania</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Temperate</t>
+        </is>
+      </c>
+      <c r="C112" s="0">
+        <v>1238422</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ghana</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Tropical</t>
+        </is>
+      </c>
+      <c r="C113" s="0">
+        <v>4681149</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>eu27</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Tropical</t>
+        </is>
+      </c>
+      <c r="C114" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>restofworld</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Tropical</t>
+        </is>
+      </c>
+      <c r="C115" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>angola</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Temperate</t>
+        </is>
+      </c>
+      <c r="C116" s="0">
+        <v>1116496</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>korea</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Tropical</t>
+        </is>
+      </c>
+      <c r="C117" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>latinamer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Boreal</t>
+        </is>
+      </c>
+      <c r="C118" s="0">
+        <v>4042587</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Temperate</t>
+        </is>
+      </c>
+      <c r="C119" s="0">
+        <v>91925063</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Tropical</t>
+        </is>
+      </c>
+      <c r="C120" s="0">
+        <v>54840655</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>WAfr</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Tropical</t>
+        </is>
+      </c>
+      <c r="C121" s="0">
+        <v>11967884</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>peru</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Boreal</t>
+        </is>
+      </c>
+      <c r="C122" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>efta</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Boreal</t>
+        </is>
+      </c>
+      <c r="C123" s="0">
+        <v>17399952</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>nigeria</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Temperate</t>
+        </is>
+      </c>
+      <c r="C124" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>seasia</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Temperate</t>
+        </is>
+      </c>
+      <c r="C125" s="0">
+        <v>1754147</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>latinamer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Temperate</t>
+        </is>
+      </c>
+      <c r="C126" s="0">
+        <v>7494430</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
           <t>paraguay</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Boreal</t>
-        </is>
-      </c>
-      <c r="C112" s="0">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Boreal</t>
+        </is>
+      </c>
+      <c r="C127" s="0">
         <v>0</v>
       </c>
     </row>
